--- a/packaging/Welcome.xlsx
+++ b/packaging/Welcome.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Benvenuto" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bilancio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Prodotti" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Grafici" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Funzioni avanzate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Welcome" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Budget" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Charts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Advanced Functions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Entrate2026">Bilancio!$B$2:$B$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Prodotti'!$A$1:$F$10</definedName>
+    <definedName name="Income2026">Budget!$B$2:$B$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Products'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -220,135 +220,134 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
           <a:bodyPr/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Entrate, uscite e saldo 2026</a:t>
+              <a:t>Income, expenses and balance 2026</a:t>
             </a:r>
           </a:p>
-        </c:rich>
-      </c:tx>
-    </c:title>
-    <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Bilancio'!B1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Budget'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-            <c:spPr>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bilancio'!$A$2:$A$13</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bilancio'!$B$2:$B$13</c:f>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Bilancio'!C1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Budget'!$A$2:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Budget'!$B$2:$B$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Budget'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-            <c:spPr>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bilancio'!$A$2:$A$13</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bilancio'!$C$2:$C$13</c:f>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Bilancio'!D1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Budget'!$A$2:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Budget'!$C$2:$C$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Budget'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-            <c:spPr>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bilancio'!$A$2:$A$13</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bilancio'!$D$2:$D$13</c:f>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Budget'!$A$2:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Budget'!$D$2:$D$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
               <a:bodyPr/>
               <a:p>
                 <a:pPr>
@@ -358,24 +357,24 @@
                   <a:t>Mese</a:t>
                 </a:r>
               </a:p>
-            </c:rich>
-          </c:tx>
-        </c:title>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:crossAx val="100"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
               <a:bodyPr/>
               <a:p>
                 <a:pPr>
@@ -385,151 +384,151 @@
                   <a:t>Euro</a:t>
                 </a:r>
               </a:p>
-            </c:rich>
-          </c:tx>
-        </c:title>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:crossAx val="10"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-</c:chartSpace>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
           <a:bodyPr/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Vendite per categoria</a:t>
+              <a:t>Sales by category</a:t>
             </a:r>
           </a:p>
-        </c:rich>
-      </c:tx>
-    </c:title>
-    <c:plotArea>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Grafici'!B1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Grafici'!$A$2:$A$5</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Grafici'!$B$2:$B$5</c:f>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-</c:chartSpace>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
           <a:bodyPr/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Vendite per categoria</a:t>
+              <a:t>Sales by category</a:t>
             </a:r>
           </a:p>
-        </c:rich>
-      </c:tx>
-    </c:title>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Grafici'!B1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Grafici'!$A$2:$A$5</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Grafici'!$B$2:$B$5</c:f>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:crossAx val="100"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
               <a:bodyPr/>
               <a:p>
                 <a:pPr>
@@ -539,21 +538,21 @@
                   <a:t>Euro</a:t>
                 </a:r>
               </a:p>
-            </c:rich>
-          </c:tx>
-        </c:title>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:crossAx val="10"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-</c:chartSpace>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,7 +563,7 @@
   <commentList>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Calcolato automaticamente come Prezzo x Quantita'.</t>
+        <t>Automatically calculated as Price x Quantity.</t>
       </text>
     </comment>
   </commentList>
@@ -572,90 +571,90 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6480000" cy="3600000"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm/>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5040000" cy="3240000"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm/>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5040000" cy="3240000"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm/>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Prodotti" displayName="Prodotti" ref="A1:F10" headerRowCount="1" totalsRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A1:F10" headerRowCount="1" totalsRowCount="1">
   <tableColumns count="6">
-    <tableColumn id="1" name="Codice"/>
-    <tableColumn id="2" name="Prodotto"/>
-    <tableColumn id="3" name="Categoria"/>
-    <tableColumn id="4" name="Prezzo"/>
-    <tableColumn id="5" name="Quantita'"/>
-    <tableColumn id="6" name="Totale" totalsRowFunction="sum"/>
+    <tableColumn id="1" name="Code"/>
+    <tableColumn id="2" name="Product"/>
+    <tableColumn id="3" name="Category"/>
+    <tableColumn id="4" name="Price"/>
+    <tableColumn id="5" name="Quantity"/>
+    <tableColumn id="6" name="Total" totalsRowFunction="sum"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -961,76 +960,76 @@
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Benvenuto in Atomo123</t>
+          <t>Welcome to Atomo123</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Il foglio di calcolo nativo per Haiku OS</t>
+          <t>The native spreadsheet for Haiku OS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Questo file e' installato insieme all'applicazione ed e' un breve giro fra le sue funzionalita':</t>
+          <t>This file is installed together with the application and is a short tour of its features:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bilancio</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Formule, un nome definito, formattazione condizionale a scala di colori, blocca riquadri, un grafico a linee</t>
+          <t>Formulas, a defined name, color-scale conditional formatting, frozen panes, a line chart</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Prodotti</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Una vera tabella strutturata Excel con riga totali, convalida dati a elenco, un commento</t>
+          <t>A real Excel structured table with a totals row, list-based data validation, a comment</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Grafici</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Grafico a barre e a torta</t>
+          <t>Bar and pie chart</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Funzioni avanzate</t>
+          <t>Advanced functions</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>UNIQUE, SORT, FILTER, SEQUENCE, INDEX/MATCH, un riferimento fra fogli diversi</t>
+          <t>UNIQUE, SORT, FILTER, SEQUENCE, INDEX/MATCH, a reference across different sheets</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Aperto/salvato/modificato tutto qui, senza toccare Excel o LibreOffice.</t>
+          <t>Opened/saved/edited entirely here, without touching Excel or LibreOffice.</t>
         </is>
       </c>
     </row>
@@ -1063,29 +1062,29 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Mese</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Entrate</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Uscite</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Saldo</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Gennaio</t>
+          <t>January</t>
         </is>
       </c>
       <c r="B2" s="9" t="n">
@@ -1102,7 +1101,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Febbraio</t>
+          <t>February</t>
         </is>
       </c>
       <c r="B3" s="9" t="n">
@@ -1119,7 +1118,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>March</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
@@ -1136,7 +1135,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Aprile</t>
+          <t>April</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -1153,7 +1152,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Maggio</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -1170,7 +1169,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Giugno</t>
+          <t>June</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -1187,7 +1186,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Luglio</t>
+          <t>July</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
@@ -1204,7 +1203,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -1221,7 +1220,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Settembre</t>
+          <t>September</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -1238,7 +1237,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Ottobre</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -1255,7 +1254,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Novembre</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
@@ -1272,7 +1271,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Dicembre</t>
+          <t>December</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
@@ -1289,11 +1288,11 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Totale annuale</t>
+          <t>Annual total</t>
         </is>
       </c>
       <c r="B14" s="11">
-        <f>SUM(Entrate2026)</f>
+        <f>SUM(Income2026)</f>
         <v/>
       </c>
       <c r="C14" s="11">
@@ -1343,32 +1342,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Codice</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Prodotto</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Categoria</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Prezzo</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Quantita'</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Totale</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1379,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tastiera meccanica</t>
+          <t>Mechanical keyboard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Elettronica</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D2" s="12" t="n">
@@ -1407,12 +1406,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mouse ottico</t>
+          <t>Optical mouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Elettronica</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D3" s="12" t="n">
@@ -1434,12 +1433,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sedia da ufficio</t>
+          <t>Office chair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D4" s="12" t="n">
@@ -1461,12 +1460,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scrivania regolabile</t>
+          <t>Adjustable desk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -1488,12 +1487,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caffe' macinato 1kg</t>
+          <t>Ground coffee 1kg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alimentari</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -1515,12 +1514,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The' verde 20 filtri</t>
+          <t>Green tea 20 bags</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alimentari</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -1542,12 +1541,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zaino porta PC</t>
+          <t>Laptop backpack</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abbigliamento</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -1569,12 +1568,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Felpa con cappuccio</t>
+          <t>Hoodie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abbigliamento</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
@@ -1591,11 +1590,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Totale</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F10" s="12">
-        <f>SUBTOTAL(109,Prodotti[Totale])</f>
+        <f>SUBTOTAL(109,Products[Total])</f>
         <v/>
       </c>
     </row>
@@ -1605,7 +1604,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C2:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Scegli una categoria dall'elenco" prompt="Seleziona una categoria" type="list">
-      <formula1>"Elettronica,Casa,Alimentari,Abbigliamento"</formula1>
+      <formula1>"Electronics,Home,Groceries,Clothing"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="1.5" right="1.5" top="2" bottom="2" header="0.5" footer="0.5"/>
@@ -1631,19 +1630,19 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Categoria</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Vendite</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Elettronica</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1653,7 +1652,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1663,7 +1662,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alimentari</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1673,7 +1672,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abbigliamento</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1707,32 +1706,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nome</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Punteggio</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nomi unici (UNIQUE)</t>
+          <t>Unique names (UNIQUE)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Ordinati per punteggio (SORT)</t>
+          <t>Sorted by score (SORT)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>&gt;= 20?</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Punteggio &gt;= 20 (FILTER)</t>
+          <t>Score &gt;= 20 (FILTER)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Sequenza (SEQUENCE)</t>
+          <t>Sequence (SEQUENCE)</t>
         </is>
       </c>
     </row>
@@ -1753,8 +1757,12 @@
         <f>_xlfn.SORT(A2:B8,2,-1)</f>
         <v/>
       </c>
+      <c r="H2">
+        <f>B2&gt;=20</f>
+        <v/>
+      </c>
       <c r="I2">
-        <f>_xlfn._xlws.FILTER(A2:A8,B2:B8&gt;=20)</f>
+        <f>_xlfn._xlws.FILTER(A2:A8,H2:H8)</f>
         <v/>
       </c>
       <c r="K2">
@@ -1771,6 +1779,10 @@
       <c r="B3" t="n">
         <v>25</v>
       </c>
+      <c r="H3">
+        <f>B3&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1781,6 +1793,10 @@
       <c r="B4" t="n">
         <v>18</v>
       </c>
+      <c r="H4">
+        <f>B4&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1791,6 +1807,10 @@
       <c r="B5" t="n">
         <v>30</v>
       </c>
+      <c r="H5">
+        <f>B5&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1801,6 +1821,10 @@
       <c r="B6" t="n">
         <v>12</v>
       </c>
+      <c r="H6">
+        <f>B6&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1811,6 +1835,10 @@
       <c r="B7" t="n">
         <v>25</v>
       </c>
+      <c r="H7">
+        <f>B7&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1821,11 +1849,15 @@
       <c r="B8" t="n">
         <v>27</v>
       </c>
+      <c r="H8">
+        <f>B8&gt;=20</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Punteggio di Elena (INDEX/MATCH):</t>
+          <t>Score for Elena (INDEX/MATCH):</t>
         </is>
       </c>
       <c r="C11">
@@ -1836,11 +1868,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saldo annuale (dal foglio 'Bilancio'):</t>
+          <t>Annual balance (from the 'Budget' sheet):</t>
         </is>
       </c>
       <c r="C13" s="12">
-        <f>Bilancio!B14-Bilancio!C14</f>
+        <f>Budget!B14-Budget!C14</f>
         <v/>
       </c>
     </row>
